--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1750000/Output_8_10.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1750000/Output_8_10.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-2018.682975847992</v>
+        <v>8599.799616861905</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5596577.414587122</v>
+        <v>5413711.842050619</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22670592.00037553</v>
+        <v>22726010.95505212</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4240077.969869662</v>
+        <v>4226612.576355352</v>
       </c>
     </row>
     <row r="11">
@@ -8670,22 +8670,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>213.4420168741263</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L11" t="n">
-        <v>227.519188839334</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M11" t="n">
-        <v>221.1696050865692</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N11" t="n">
-        <v>220.0879480187015</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>221.2927692106315</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P11" t="n">
-        <v>223.7177545492394</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8746,28 +8746,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>124.1958059119497</v>
+        <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>133.3261465215288</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L12" t="n">
-        <v>132.4830118553459</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M12" t="n">
-        <v>135.0490339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
-        <v>124.0691932154088</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>135.9433104821803</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>128.6348413765944</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
-        <v>136.4124155954555</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,19 +8831,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>131.3993975927137</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M13" t="n">
-        <v>135.251046242687</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N13" t="n">
-        <v>124.0981838094955</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O13" t="n">
-        <v>135.1430302551215</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P13" t="n">
-        <v>134.892725360623</v>
+        <v>135.0065633140411</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8907,22 +8907,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>213.4420168741263</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L14" t="n">
-        <v>227.519188839334</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M14" t="n">
-        <v>221.1696050865692</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N14" t="n">
-        <v>220.0879480187015</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>221.2927692106315</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P14" t="n">
-        <v>223.7177545492394</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8983,28 +8983,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>124.1958059119497</v>
+        <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>133.3261465215288</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L15" t="n">
-        <v>132.4830118553459</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
-        <v>135.0490339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N15" t="n">
-        <v>124.0691932154088</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>135.9433104821803</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>128.6348413765944</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
-        <v>136.4124155954555</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,19 +9068,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>131.3993975927137</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M16" t="n">
-        <v>135.251046242687</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N16" t="n">
-        <v>124.0981838094955</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O16" t="n">
-        <v>135.1430302551215</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P16" t="n">
-        <v>134.892725360623</v>
+        <v>135.0065633140411</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>213.4420168741263</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L17" t="n">
-        <v>227.519188839334</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M17" t="n">
-        <v>221.1696050865692</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N17" t="n">
-        <v>220.0879480187015</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O17" t="n">
-        <v>221.2927692106315</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P17" t="n">
-        <v>223.7177545492394</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9220,28 +9220,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>124.1958059119497</v>
+        <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>133.3261465215288</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
-        <v>132.4830118553459</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>135.0490339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N18" t="n">
-        <v>124.0691932154088</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
-        <v>135.9433104821803</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>128.6348413765944</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
-        <v>136.4124155954555</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9305,19 +9305,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L19" t="n">
-        <v>131.3993975927137</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M19" t="n">
-        <v>135.251046242687</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N19" t="n">
-        <v>124.0981838094955</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O19" t="n">
-        <v>135.1430302551215</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P19" t="n">
-        <v>134.892725360623</v>
+        <v>135.0065633140411</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9381,22 +9381,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>213.4420168741263</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L20" t="n">
-        <v>227.519188839334</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M20" t="n">
-        <v>221.1696050865692</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N20" t="n">
-        <v>220.0879480187015</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O20" t="n">
-        <v>221.2927692106315</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P20" t="n">
-        <v>223.7177545492394</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q20" t="n">
         <v>212.3149906599047</v>
@@ -9457,28 +9457,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>124.1958059119497</v>
+        <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>133.3261465215288</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
-        <v>132.4830118553459</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M21" t="n">
-        <v>135.0490339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N21" t="n">
-        <v>124.0691932154088</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>135.9433104821803</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>128.6348413765944</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
-        <v>136.4124155954555</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9542,19 +9542,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L22" t="n">
-        <v>131.3993975927137</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M22" t="n">
-        <v>135.251046242687</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N22" t="n">
-        <v>124.0981838094955</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O22" t="n">
-        <v>135.1430302551215</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P22" t="n">
-        <v>134.892725360623</v>
+        <v>135.0065633140411</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9618,22 +9618,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>213.4420168741263</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L23" t="n">
-        <v>227.519188839334</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M23" t="n">
-        <v>221.1696050865692</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N23" t="n">
-        <v>220.0879480187015</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O23" t="n">
-        <v>221.2927692106315</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P23" t="n">
-        <v>223.7177545492394</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q23" t="n">
         <v>212.3149906599047</v>
@@ -9694,28 +9694,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>124.1958059119497</v>
+        <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>133.3261465215288</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>132.4830118553459</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
-        <v>135.0490339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N24" t="n">
-        <v>124.0691932154088</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>135.9433104821803</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
-        <v>128.6348413765944</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q24" t="n">
-        <v>136.4124155954555</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9779,19 +9779,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L25" t="n">
-        <v>131.3993975927137</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M25" t="n">
-        <v>135.251046242687</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N25" t="n">
-        <v>124.0981838094955</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O25" t="n">
-        <v>135.1430302551215</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P25" t="n">
-        <v>134.892725360623</v>
+        <v>135.0065633140411</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9855,22 +9855,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>213.4420168741263</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L26" t="n">
-        <v>227.519188839334</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M26" t="n">
-        <v>221.1696050865692</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N26" t="n">
-        <v>220.0879480187015</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O26" t="n">
-        <v>221.2927692106315</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P26" t="n">
-        <v>223.7177545492394</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q26" t="n">
         <v>212.3149906599047</v>
@@ -9931,28 +9931,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>124.1958059119497</v>
+        <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>133.3261465215288</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
-        <v>132.4830118553459</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
-        <v>135.0490339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N27" t="n">
-        <v>124.0691932154088</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>135.9433104821803</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>128.6348413765944</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
-        <v>136.4124155954555</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10016,19 +10016,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L28" t="n">
-        <v>131.3993975927137</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M28" t="n">
-        <v>135.251046242687</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N28" t="n">
-        <v>124.0981838094955</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O28" t="n">
-        <v>135.1430302551215</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P28" t="n">
-        <v>134.892725360623</v>
+        <v>135.0065633140411</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10092,22 +10092,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>213.4420168741263</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L29" t="n">
-        <v>227.519188839334</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M29" t="n">
-        <v>221.1696050865692</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N29" t="n">
-        <v>220.0879480187015</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O29" t="n">
-        <v>221.2927692106315</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P29" t="n">
-        <v>223.7177545492394</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10168,28 +10168,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>124.1958059119497</v>
+        <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>133.3261465215288</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L30" t="n">
-        <v>132.4830118553459</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>135.0490339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
-        <v>124.0691932154088</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>135.9433104821803</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
-        <v>128.6348413765944</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q30" t="n">
-        <v>136.4124155954555</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10253,19 +10253,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L31" t="n">
-        <v>131.3993975927137</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M31" t="n">
-        <v>135.251046242687</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N31" t="n">
-        <v>124.0981838094955</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O31" t="n">
-        <v>135.1430302551215</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P31" t="n">
-        <v>134.892725360623</v>
+        <v>135.0065633140411</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10329,22 +10329,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>213.4420168741263</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L32" t="n">
-        <v>227.519188839334</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M32" t="n">
-        <v>221.1696050865692</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N32" t="n">
-        <v>220.0879480187015</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O32" t="n">
-        <v>221.2927692106315</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P32" t="n">
-        <v>223.7177545492394</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10405,28 +10405,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>124.1958059119497</v>
+        <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>133.3261465215288</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
-        <v>132.4830118553459</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
-        <v>135.0490339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N33" t="n">
-        <v>124.0691932154088</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>135.9433104821803</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
-        <v>128.6348413765944</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q33" t="n">
-        <v>136.4124155954555</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10490,19 +10490,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L34" t="n">
-        <v>131.3993975927137</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M34" t="n">
-        <v>135.251046242687</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N34" t="n">
-        <v>124.0981838094955</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O34" t="n">
-        <v>135.1430302551215</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P34" t="n">
-        <v>134.892725360623</v>
+        <v>135.0065633140411</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10566,22 +10566,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>213.4420168741263</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L35" t="n">
-        <v>227.519188839334</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M35" t="n">
-        <v>221.1696050865692</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N35" t="n">
-        <v>220.0879480187015</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O35" t="n">
-        <v>221.2927692106315</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P35" t="n">
-        <v>223.7177545492394</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10642,28 +10642,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>124.1958059119497</v>
+        <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>133.3261465215288</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>132.4830118553459</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
-        <v>135.0490339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N36" t="n">
-        <v>124.0691932154088</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>135.9433104821803</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>128.6348413765944</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q36" t="n">
-        <v>136.4124155954555</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10727,19 +10727,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L37" t="n">
-        <v>131.3993975927137</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M37" t="n">
-        <v>135.251046242687</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N37" t="n">
-        <v>124.0981838094955</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O37" t="n">
-        <v>135.1430302551215</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P37" t="n">
-        <v>134.892725360623</v>
+        <v>135.0065633140411</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10803,22 +10803,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>213.4420168741263</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L38" t="n">
-        <v>227.519188839334</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M38" t="n">
-        <v>221.1696050865692</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N38" t="n">
-        <v>220.0879480187015</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O38" t="n">
-        <v>221.2927692106315</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P38" t="n">
-        <v>223.7177545492394</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q38" t="n">
         <v>212.3149906599047</v>
@@ -10879,28 +10879,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>124.1958059119497</v>
+        <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>133.3261465215288</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>132.4830118553459</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M39" t="n">
-        <v>135.0490339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
-        <v>124.0691932154088</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>135.9433104821803</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>128.6348413765944</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
-        <v>136.4124155954555</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10964,19 +10964,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L40" t="n">
-        <v>131.3993975927137</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M40" t="n">
-        <v>135.251046242687</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N40" t="n">
-        <v>124.0981838094955</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O40" t="n">
-        <v>135.1430302551215</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P40" t="n">
-        <v>134.892725360623</v>
+        <v>135.0065633140411</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11040,22 +11040,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>213.4420168741263</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L41" t="n">
-        <v>227.519188839334</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M41" t="n">
-        <v>221.1696050865692</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N41" t="n">
-        <v>220.0879480187015</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O41" t="n">
-        <v>221.2927692106315</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P41" t="n">
-        <v>223.7177545492394</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11116,28 +11116,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>124.1958059119497</v>
+        <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>133.3261465215288</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>132.4830118553459</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M42" t="n">
-        <v>135.0490339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N42" t="n">
-        <v>124.0691932154088</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>135.9433104821803</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>128.6348413765944</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q42" t="n">
-        <v>136.4124155954555</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11201,19 +11201,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L43" t="n">
-        <v>131.3993975927137</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M43" t="n">
-        <v>135.251046242687</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N43" t="n">
-        <v>124.0981838094955</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O43" t="n">
-        <v>135.1430302551215</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P43" t="n">
-        <v>134.892725360623</v>
+        <v>135.0065633140411</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11277,22 +11277,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K44" t="n">
-        <v>213.4420168741263</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L44" t="n">
-        <v>227.519188839334</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M44" t="n">
-        <v>221.1696050865692</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N44" t="n">
-        <v>220.0879480187015</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O44" t="n">
-        <v>221.2927692106315</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P44" t="n">
-        <v>223.7177545492394</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q44" t="n">
         <v>212.3149906599047</v>
@@ -11353,28 +11353,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>124.1958059119497</v>
+        <v>126.0910353404088</v>
       </c>
       <c r="K45" t="n">
-        <v>133.3261465215288</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L45" t="n">
-        <v>132.4830118553459</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M45" t="n">
-        <v>135.0490339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N45" t="n">
-        <v>124.0691932154088</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O45" t="n">
-        <v>135.9433104821803</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P45" t="n">
-        <v>128.6348413765944</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q45" t="n">
-        <v>136.4124155954555</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11438,19 +11438,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L46" t="n">
-        <v>131.3993975927137</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M46" t="n">
-        <v>135.251046242687</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N46" t="n">
-        <v>124.0981838094955</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O46" t="n">
-        <v>135.1430302551215</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P46" t="n">
-        <v>134.892725360623</v>
+        <v>135.0065633140411</v>
       </c>
       <c r="Q46" t="n">
         <v>65.34295837775146</v>
@@ -23230,16 +23230,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>415.2504762086024</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H11" t="n">
-        <v>338.9395810102395</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I11" t="n">
-        <v>208.4610855503054</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J11" t="n">
-        <v>7.513676289285883</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -23260,19 +23260,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.347066048715659</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>146.5862586446673</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S11" t="n">
-        <v>207.8291650636323</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T11" t="n">
-        <v>222.8670756947846</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U11" t="n">
-        <v>251.3414720033139</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,16 +23309,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>137.3155548990597</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H12" t="n">
-        <v>111.9653876327229</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I12" t="n">
-        <v>88.43389700235848</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>98.42172094509596</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S12" t="n">
-        <v>171.163784311385</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T12" t="n">
-        <v>200.0520211476518</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9395424583333</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,19 +23388,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.9675367355079</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H13" t="n">
-        <v>162.0187462779314</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I13" t="n">
-        <v>154.7454913207009</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J13" t="n">
-        <v>91.70178667404983</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K13" t="n">
-        <v>19.5458852685058</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23415,22 +23415,22 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>84.19904325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R13" t="n">
-        <v>176.239325803399</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S13" t="n">
-        <v>223.6080570533657</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T13" t="n">
-        <v>227.8454254938553</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U13" t="n">
-        <v>286.3177506679663</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,16 +23467,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>415.2504762086024</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H14" t="n">
-        <v>338.9395810102395</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I14" t="n">
-        <v>208.4610855503054</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J14" t="n">
-        <v>7.513676289285883</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -23497,19 +23497,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.347066048715659</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>146.5862586446673</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S14" t="n">
-        <v>207.8291650636323</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T14" t="n">
-        <v>222.8670756947846</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U14" t="n">
-        <v>251.3414720033139</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,16 +23546,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>137.3155548990597</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H15" t="n">
-        <v>111.9653876327229</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I15" t="n">
-        <v>88.43389700235848</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>98.42172094509596</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S15" t="n">
-        <v>171.163784311385</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T15" t="n">
-        <v>200.0520211476518</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9395424583333</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,19 +23625,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.9675367355079</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H16" t="n">
-        <v>162.0187462779314</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I16" t="n">
-        <v>154.7454913207009</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J16" t="n">
-        <v>91.70178667404983</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>19.5458852685058</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23652,22 +23652,22 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>84.19904325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
-        <v>176.239325803399</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S16" t="n">
-        <v>223.6080570533657</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T16" t="n">
-        <v>227.8454254938553</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U16" t="n">
-        <v>286.3177506679663</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,16 +23704,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>415.2504762086024</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H17" t="n">
-        <v>338.9395810102395</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I17" t="n">
-        <v>208.4610855503054</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J17" t="n">
-        <v>7.513676289285883</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -23734,19 +23734,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.347066048715659</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>146.5862586446673</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S17" t="n">
-        <v>207.8291650636323</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T17" t="n">
-        <v>222.8670756947846</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U17" t="n">
-        <v>251.3414720033139</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,16 +23783,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>137.3155548990597</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H18" t="n">
-        <v>111.9653876327229</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I18" t="n">
-        <v>88.43389700235848</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>98.42172094509596</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S18" t="n">
-        <v>171.163784311385</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T18" t="n">
-        <v>200.0520211476518</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9395424583333</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,19 +23862,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.9675367355079</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H19" t="n">
-        <v>162.0187462779314</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I19" t="n">
-        <v>154.7454913207009</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J19" t="n">
-        <v>91.70178667404983</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K19" t="n">
-        <v>19.5458852685058</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -23889,22 +23889,22 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q19" t="n">
-        <v>84.19904325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>176.239325803399</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S19" t="n">
-        <v>223.6080570533657</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T19" t="n">
-        <v>227.8454254938553</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U19" t="n">
-        <v>286.3177506679663</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,16 +23941,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>415.2504762086024</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H20" t="n">
-        <v>338.9395810102395</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I20" t="n">
-        <v>208.4610855503054</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J20" t="n">
-        <v>7.513676289285883</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -23971,19 +23971,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.347066048715659</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>146.5862586446673</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
-        <v>207.8291650636323</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
-        <v>222.8670756947846</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
-        <v>251.3414720033139</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,16 +24020,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>137.3155548990597</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
-        <v>111.9653876327229</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I21" t="n">
-        <v>88.43389700235848</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>98.42172094509596</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
-        <v>171.163784311385</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>200.0520211476518</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9395424583333</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,19 +24099,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.9675367355079</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H22" t="n">
-        <v>162.0187462779314</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I22" t="n">
-        <v>154.7454913207009</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J22" t="n">
-        <v>91.70178667404983</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K22" t="n">
-        <v>19.5458852685058</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -24126,22 +24126,22 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q22" t="n">
-        <v>84.19904325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R22" t="n">
-        <v>176.239325803399</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S22" t="n">
-        <v>223.6080570533657</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T22" t="n">
-        <v>227.8454254938553</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U22" t="n">
-        <v>286.3177506679663</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,16 +24178,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>415.2504762086024</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
-        <v>338.9395810102395</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I23" t="n">
-        <v>208.4610855503054</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J23" t="n">
-        <v>7.513676289285883</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -24208,19 +24208,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.347066048715659</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>146.5862586446673</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S23" t="n">
-        <v>207.8291650636323</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
-        <v>222.8670756947846</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U23" t="n">
-        <v>251.3414720033139</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,16 +24257,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3155548990597</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
-        <v>111.9653876327229</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I24" t="n">
-        <v>88.43389700235848</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>98.42172094509596</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
-        <v>171.163784311385</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>200.0520211476518</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9395424583333</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,19 +24336,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.9675367355079</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H25" t="n">
-        <v>162.0187462779314</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I25" t="n">
-        <v>154.7454913207009</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J25" t="n">
-        <v>91.70178667404983</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K25" t="n">
-        <v>19.5458852685058</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -24363,22 +24363,22 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q25" t="n">
-        <v>84.19904325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>176.239325803399</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S25" t="n">
-        <v>223.6080570533657</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T25" t="n">
-        <v>227.8454254938553</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U25" t="n">
-        <v>286.3177506679663</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,16 +24415,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>415.2504762086024</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H26" t="n">
-        <v>338.9395810102395</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I26" t="n">
-        <v>208.4610855503054</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J26" t="n">
-        <v>7.513676289285883</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -24445,19 +24445,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.347066048715659</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>146.5862586446673</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
-        <v>207.8291650636323</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T26" t="n">
-        <v>222.8670756947846</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>251.3414720033139</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,16 +24494,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>137.3155548990597</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H27" t="n">
-        <v>111.9653876327229</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I27" t="n">
-        <v>88.43389700235848</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>98.42172094509596</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
-        <v>171.163784311385</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>200.0520211476518</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9395424583333</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,19 +24573,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.9675367355079</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H28" t="n">
-        <v>162.0187462779314</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I28" t="n">
-        <v>154.7454913207009</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J28" t="n">
-        <v>91.70178667404983</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K28" t="n">
-        <v>19.5458852685058</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -24600,22 +24600,22 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q28" t="n">
-        <v>84.19904325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R28" t="n">
-        <v>176.239325803399</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S28" t="n">
-        <v>223.6080570533657</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T28" t="n">
-        <v>227.8454254938553</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U28" t="n">
-        <v>286.3177506679663</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,16 +24652,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>415.2504762086024</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H29" t="n">
-        <v>338.9395810102395</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I29" t="n">
-        <v>208.4610855503054</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J29" t="n">
-        <v>7.513676289285883</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -24682,19 +24682,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.347066048715659</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>146.5862586446673</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S29" t="n">
-        <v>207.8291650636323</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>222.8670756947846</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
-        <v>251.3414720033139</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,16 +24731,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3155548990597</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
-        <v>111.9653876327229</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
-        <v>88.43389700235848</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>98.42172094509596</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>171.163784311385</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T30" t="n">
-        <v>200.0520211476518</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9395424583333</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,19 +24810,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.9675367355079</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H31" t="n">
-        <v>162.0187462779314</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I31" t="n">
-        <v>154.7454913207009</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J31" t="n">
-        <v>91.70178667404983</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K31" t="n">
-        <v>19.5458852685058</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -24837,22 +24837,22 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q31" t="n">
-        <v>84.19904325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
-        <v>176.239325803399</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S31" t="n">
-        <v>223.6080570533657</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T31" t="n">
-        <v>227.8454254938553</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U31" t="n">
-        <v>286.3177506679663</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,16 +24889,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>415.2504762086024</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H32" t="n">
-        <v>338.9395810102395</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I32" t="n">
-        <v>208.4610855503054</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J32" t="n">
-        <v>7.513676289285883</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -24919,19 +24919,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.347066048715659</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>146.5862586446673</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
-        <v>207.8291650636323</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>222.8670756947846</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
-        <v>251.3414720033139</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,16 +24968,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3155548990597</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>111.9653876327229</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
-        <v>88.43389700235848</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>98.42172094509596</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>171.163784311385</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
-        <v>200.0520211476518</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9395424583333</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,19 +25047,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.9675367355079</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H34" t="n">
-        <v>162.0187462779314</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I34" t="n">
-        <v>154.7454913207009</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J34" t="n">
-        <v>91.70178667404983</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K34" t="n">
-        <v>19.5458852685058</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -25074,22 +25074,22 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q34" t="n">
-        <v>84.19904325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
-        <v>176.239325803399</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S34" t="n">
-        <v>223.6080570533657</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T34" t="n">
-        <v>227.8454254938553</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U34" t="n">
-        <v>286.3177506679663</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,16 +25126,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>415.2504762086024</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
-        <v>338.9395810102395</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I35" t="n">
-        <v>208.4610855503054</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J35" t="n">
-        <v>7.513676289285883</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -25156,19 +25156,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.347066048715659</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>146.5862586446673</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S35" t="n">
-        <v>207.8291650636323</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T35" t="n">
-        <v>222.8670756947846</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U35" t="n">
-        <v>251.3414720033139</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,16 +25205,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>137.3155548990597</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H36" t="n">
-        <v>111.9653876327229</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I36" t="n">
-        <v>88.43389700235848</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>98.42172094509596</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>171.163784311385</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
-        <v>200.0520211476518</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9395424583333</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,19 +25284,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.9675367355079</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H37" t="n">
-        <v>162.0187462779314</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I37" t="n">
-        <v>154.7454913207009</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J37" t="n">
-        <v>91.70178667404983</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K37" t="n">
-        <v>19.5458852685058</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -25311,22 +25311,22 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q37" t="n">
-        <v>84.19904325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>176.239325803399</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S37" t="n">
-        <v>223.6080570533657</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T37" t="n">
-        <v>227.8454254938553</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U37" t="n">
-        <v>286.3177506679663</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,16 +25363,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>415.2504762086024</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H38" t="n">
-        <v>338.9395810102395</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I38" t="n">
-        <v>208.4610855503054</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J38" t="n">
-        <v>7.513676289285883</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25393,19 +25393,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.347066048715659</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>146.5862586446673</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>207.8291650636323</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
-        <v>222.8670756947846</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>251.3414720033139</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,16 +25442,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>137.3155548990597</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
-        <v>111.9653876327229</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
-        <v>88.43389700235848</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>98.42172094509596</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>171.163784311385</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>200.0520211476518</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9395424583333</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,19 +25521,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.9675367355079</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H40" t="n">
-        <v>162.0187462779314</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I40" t="n">
-        <v>154.7454913207009</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J40" t="n">
-        <v>91.70178667404983</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K40" t="n">
-        <v>19.5458852685058</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -25548,22 +25548,22 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q40" t="n">
-        <v>84.19904325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>176.239325803399</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S40" t="n">
-        <v>223.6080570533657</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T40" t="n">
-        <v>227.8454254938553</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>286.3177506679663</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,16 +25600,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>415.2504762086024</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H41" t="n">
-        <v>338.9395810102395</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I41" t="n">
-        <v>208.4610855503054</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J41" t="n">
-        <v>7.513676289285883</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -25630,19 +25630,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.347066048715659</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>146.5862586446673</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S41" t="n">
-        <v>207.8291650636323</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T41" t="n">
-        <v>222.8670756947846</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U41" t="n">
-        <v>251.3414720033139</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,16 +25679,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>137.3155548990597</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>111.9653876327229</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
-        <v>88.43389700235848</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>98.42172094509596</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>171.163784311385</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
-        <v>200.0520211476518</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9395424583333</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,19 +25758,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.9675367355079</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H43" t="n">
-        <v>162.0187462779314</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I43" t="n">
-        <v>154.7454913207009</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J43" t="n">
-        <v>91.70178667404983</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K43" t="n">
-        <v>19.5458852685058</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -25785,22 +25785,22 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q43" t="n">
-        <v>84.19904325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
-        <v>176.239325803399</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S43" t="n">
-        <v>223.6080570533657</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T43" t="n">
-        <v>227.8454254938553</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U43" t="n">
-        <v>286.3177506679663</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,16 +25837,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>415.2504762086024</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H44" t="n">
-        <v>338.9395810102395</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I44" t="n">
-        <v>208.4610855503054</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J44" t="n">
-        <v>7.513676289285883</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -25867,19 +25867,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.347066048715659</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R44" t="n">
-        <v>146.5862586446673</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S44" t="n">
-        <v>207.8291650636323</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T44" t="n">
-        <v>222.8670756947846</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U44" t="n">
-        <v>251.3414720033139</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,16 +25916,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>137.3155548990597</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H45" t="n">
-        <v>111.9653876327229</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I45" t="n">
-        <v>88.43389700235848</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>98.42172094509596</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S45" t="n">
-        <v>171.163784311385</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T45" t="n">
-        <v>200.0520211476518</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9395424583333</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,19 +25995,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.9675367355079</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H46" t="n">
-        <v>162.0187462779314</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I46" t="n">
-        <v>154.7454913207009</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J46" t="n">
-        <v>91.70178667404983</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K46" t="n">
-        <v>19.5458852685058</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -26022,22 +26022,22 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q46" t="n">
-        <v>84.19904325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R46" t="n">
-        <v>176.239325803399</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S46" t="n">
-        <v>223.6080570533657</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T46" t="n">
-        <v>227.8454254938553</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U46" t="n">
-        <v>286.3177506679663</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>367077.0227238379</v>
+        <v>365525.1788069177</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>367077.0227238379</v>
+        <v>365525.1788069177</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>367077.0227238379</v>
+        <v>365525.1788069177</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>367077.0227238379</v>
+        <v>365525.1788069177</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>367077.0227238379</v>
+        <v>365525.1788069177</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>367077.0227238379</v>
+        <v>365525.1788069177</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>367077.0227238379</v>
+        <v>365525.1788069177</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>367077.0227238379</v>
+        <v>365525.1788069177</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>367077.0227238379</v>
+        <v>365525.1788069177</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>367077.0227238379</v>
+        <v>365525.1788069177</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>367077.0227238379</v>
+        <v>365525.1788069177</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>367077.0227238379</v>
+        <v>365525.1788069177</v>
       </c>
     </row>
   </sheetData>
@@ -26270,40 +26270,40 @@
         <v>53753.70276572321</v>
       </c>
       <c r="E2" t="n">
-        <v>54215.52738802824</v>
+        <v>53753.70276572321</v>
       </c>
       <c r="F2" t="n">
-        <v>54215.52738802824</v>
+        <v>53753.70276572321</v>
       </c>
       <c r="G2" t="n">
-        <v>54215.52738802824</v>
+        <v>53753.70276572321</v>
       </c>
       <c r="H2" t="n">
-        <v>54215.52738802824</v>
+        <v>53753.70276572321</v>
       </c>
       <c r="I2" t="n">
-        <v>54215.52738802824</v>
+        <v>53753.70276572321</v>
       </c>
       <c r="J2" t="n">
-        <v>54215.52738802824</v>
+        <v>53753.70276572321</v>
       </c>
       <c r="K2" t="n">
-        <v>54215.52738802824</v>
+        <v>53753.70276572321</v>
       </c>
       <c r="L2" t="n">
-        <v>54215.52738802824</v>
+        <v>53753.70276572321</v>
       </c>
       <c r="M2" t="n">
-        <v>54215.52738802824</v>
+        <v>53753.70276572321</v>
       </c>
       <c r="N2" t="n">
-        <v>54215.52738802824</v>
+        <v>53753.7027657232</v>
       </c>
       <c r="O2" t="n">
-        <v>54215.52738802824</v>
+        <v>53753.70276572321</v>
       </c>
       <c r="P2" t="n">
-        <v>54215.52738802824</v>
+        <v>53753.70276572321</v>
       </c>
     </row>
     <row r="3">
@@ -26322,7 +26322,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>10444.239</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43002.96221257856</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="C4" t="n">
-        <v>43002.96221257856</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="D4" t="n">
-        <v>43002.96221257856</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="E4" t="n">
-        <v>41783.85839566849</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="F4" t="n">
-        <v>41783.85839566849</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="G4" t="n">
-        <v>41783.85839566849</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="H4" t="n">
-        <v>41783.85839566849</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="I4" t="n">
-        <v>41783.85839566849</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="J4" t="n">
-        <v>41783.85839566849</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="K4" t="n">
-        <v>41783.85839566849</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="L4" t="n">
-        <v>41783.85839566849</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="M4" t="n">
-        <v>41783.85839566849</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="N4" t="n">
-        <v>41783.85839566849</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="O4" t="n">
-        <v>41783.85839566849</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="P4" t="n">
-        <v>41783.85839566849</v>
+        <v>41731.10116290394</v>
       </c>
     </row>
     <row r="5">
@@ -26426,40 +26426,40 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>283.4</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>283.4</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>283.4</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>283.4</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>283.4</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>283.4</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>283.4</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>283.4</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>283.4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>283.4</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>283.4</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>283.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-22876.85944685535</v>
+        <v>-21604.99839718073</v>
       </c>
       <c r="C6" t="n">
-        <v>-22876.85944685535</v>
+        <v>-21604.99839718073</v>
       </c>
       <c r="D6" t="n">
-        <v>-22876.85944685535</v>
+        <v>-21604.99839718073</v>
       </c>
       <c r="E6" t="n">
-        <v>1704.02999235975</v>
+        <v>12022.60160281927</v>
       </c>
       <c r="F6" t="n">
-        <v>12148.26899235975</v>
+        <v>12022.60160281927</v>
       </c>
       <c r="G6" t="n">
-        <v>12148.26899235975</v>
+        <v>12022.60160281927</v>
       </c>
       <c r="H6" t="n">
-        <v>12148.26899235975</v>
+        <v>12022.60160281927</v>
       </c>
       <c r="I6" t="n">
-        <v>12148.26899235975</v>
+        <v>12022.60160281927</v>
       </c>
       <c r="J6" t="n">
-        <v>12148.26899235975</v>
+        <v>12022.60160281927</v>
       </c>
       <c r="K6" t="n">
-        <v>12148.26899235975</v>
+        <v>12022.60160281927</v>
       </c>
       <c r="L6" t="n">
-        <v>12148.26899235975</v>
+        <v>12022.60160281927</v>
       </c>
       <c r="M6" t="n">
-        <v>12148.26899235975</v>
+        <v>12022.60160281927</v>
       </c>
       <c r="N6" t="n">
-        <v>12148.26899235975</v>
+        <v>12022.60160281925</v>
       </c>
       <c r="O6" t="n">
-        <v>12148.26899235975</v>
+        <v>12022.60160281927</v>
       </c>
       <c r="P6" t="n">
-        <v>12148.26899235975</v>
+        <v>12022.60160281927</v>
       </c>
     </row>
   </sheetData>
@@ -26684,40 +26684,40 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26901,7 +26901,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.05226130653266328</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5352211055276379</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.014804020100503</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4.435613065326634</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>6.647834170854272</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>8.247226130653267</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>9.176628140703517</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>9.325115577889449</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>8.805442211055276</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7.515241206030151</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.643633165829145</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.282859296482413</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.190904522613066</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2287738693467336</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.004180904522613061</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,49 +31749,49 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0279622641509434</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.270056603773585</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9627358490566039</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.641820754716981</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>4.515292452830189</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>6.071367924528302</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>7.084999999999999</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7.272518867924529</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6.652933962264151</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>5.33956603773585</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.569358490566038</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.736113207547171</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5193867924528298</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1127075471698113</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.001839622641509435</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02344262295081967</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2084262295081968</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7049836065573772</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.657393442622951</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.723606557377048</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3.48527868852459</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.674737704918032</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.587360655737707</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.313508196721312</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.835278688524589</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.963</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.054065573770491</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4085409836065572</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1001639344262295</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.001278688524590165</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05226130653266328</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5352211055276379</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2.014804020100503</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>4.435613065326634</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>6.647834170854272</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>8.247226130653267</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>9.176628140703517</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>9.325115577889449</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>8.805442211055276</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>7.515241206030151</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.643633165829145</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.282859296482413</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.190904522613066</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2287738693467336</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.004180904522613061</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,49 +31986,49 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0279622641509434</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.270056603773585</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9627358490566039</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.641820754716981</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>4.515292452830189</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>6.071367924528302</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>7.084999999999999</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>7.272518867924529</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>6.652933962264151</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>5.33956603773585</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.569358490566038</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.736113207547171</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5193867924528298</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1127075471698113</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.001839622641509435</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.02344262295081967</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2084262295081968</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7049836065573772</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.657393442622951</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2.723606557377048</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3.48527868852459</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.674737704918032</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.587360655737707</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.313508196721312</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.835278688524589</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.963</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.054065573770491</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4085409836065572</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1001639344262295</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.001278688524590165</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05226130653266328</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5352211055276379</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2.014804020100503</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>4.435613065326634</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>6.647834170854272</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>8.247226130653267</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>9.176628140703517</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>9.325115577889449</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>8.805442211055276</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>7.515241206030151</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.643633165829145</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.282859296482413</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.190904522613066</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2287738693467336</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.004180904522613061</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,49 +32223,49 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0279622641509434</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.270056603773585</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9627358490566039</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.641820754716981</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>4.515292452830189</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>6.071367924528302</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>7.084999999999999</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>7.272518867924529</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>6.652933962264151</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>5.33956603773585</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.569358490566038</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.736113207547171</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5193867924528298</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1127075471698113</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.001839622641509435</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.02344262295081967</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2084262295081968</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7049836065573772</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.657393442622951</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>2.723606557377048</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>3.48527868852459</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.674737704918032</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.587360655737707</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.313508196721312</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.835278688524589</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.963</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.054065573770491</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4085409836065572</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1001639344262295</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.001278688524590165</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05226130653266328</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5352211055276379</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2.014804020100503</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>4.435613065326634</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>6.647834170854272</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>8.247226130653267</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>9.176628140703517</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>9.325115577889449</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>8.805442211055276</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>7.515241206030151</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.643633165829145</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.282859296482413</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.190904522613066</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2287738693467336</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.004180904522613061</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,49 +32460,49 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0279622641509434</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.270056603773585</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9627358490566039</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.641820754716981</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>4.515292452830189</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>6.071367924528302</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>7.084999999999999</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>7.272518867924529</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>6.652933962264151</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>5.33956603773585</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.569358490566038</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.736113207547171</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5193867924528298</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1127075471698113</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.001839622641509435</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02344262295081967</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2084262295081968</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7049836065573772</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1.657393442622951</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>2.723606557377048</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>3.48527868852459</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.674737704918032</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.587360655737707</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.313508196721312</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.835278688524589</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.963</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.054065573770491</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4085409836065572</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1001639344262295</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.001278688524590165</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.05226130653266328</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5352211055276379</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>2.014804020100503</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>4.435613065326634</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>6.647834170854272</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>8.247226130653267</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>9.176628140703517</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>9.325115577889449</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>8.805442211055276</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>7.515241206030151</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.643633165829145</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.282859296482413</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.190904522613066</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2287738693467336</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.004180904522613061</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,49 +32697,49 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0279622641509434</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.270056603773585</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9627358490566039</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2.641820754716981</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>4.515292452830189</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>6.071367924528302</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>7.084999999999999</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>7.272518867924529</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>6.652933962264151</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>5.33956603773585</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.569358490566038</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.736113207547171</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5193867924528298</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1127075471698113</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0.001839622641509435</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.02344262295081967</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2084262295081968</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7049836065573772</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1.657393442622951</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>2.723606557377048</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>3.48527868852459</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.674737704918032</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.587360655737707</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.313508196721312</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.835278688524589</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.963</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.054065573770491</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4085409836065572</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1001639344262295</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0.001278688524590165</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.05226130653266328</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5352211055276379</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2.014804020100503</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>4.435613065326634</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>6.647834170854272</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>8.247226130653267</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>9.176628140703517</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>9.325115577889449</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>8.805442211055276</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>7.515241206030151</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.643633165829145</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.282859296482413</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.190904522613066</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2287738693467336</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0.004180904522613061</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,49 +32934,49 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0279622641509434</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.270056603773585</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9627358490566039</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2.641820754716981</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>4.515292452830189</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>6.071367924528302</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>7.084999999999999</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>7.272518867924529</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>6.652933962264151</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>5.33956603773585</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.569358490566038</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.736113207547171</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.5193867924528298</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1127075471698113</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0.001839622641509435</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.02344262295081967</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2084262295081968</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7049836065573772</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1.657393442622951</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>2.723606557377048</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3.48527868852459</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.674737704918032</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.587360655737707</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.313508196721312</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.835278688524589</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.963</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.054065573770491</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.4085409836065572</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1001639344262295</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0.001278688524590165</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.05226130653266328</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5352211055276379</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>2.014804020100503</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>4.435613065326634</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>6.647834170854272</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>8.247226130653267</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>9.176628140703517</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>9.325115577889449</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>8.805442211055276</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>7.515241206030151</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.643633165829145</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.282859296482413</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.190904522613066</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2287738693467336</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0.004180904522613061</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,49 +33171,49 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0279622641509434</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.270056603773585</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9627358490566039</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>2.641820754716981</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>4.515292452830189</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>6.071367924528302</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>7.084999999999999</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>7.272518867924529</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>6.652933962264151</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>5.33956603773585</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.569358490566038</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.736113207547171</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.5193867924528298</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1127075471698113</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0.001839622641509435</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02344262295081967</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2084262295081968</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7049836065573772</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1.657393442622951</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>2.723606557377048</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>3.48527868852459</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.674737704918032</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.587360655737707</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.313508196721312</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.835278688524589</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.963</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.054065573770491</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.4085409836065572</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1001639344262295</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0.001278688524590165</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.05226130653266328</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5352211055276379</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2.014804020100503</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>4.435613065326634</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>6.647834170854272</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>8.247226130653267</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>9.176628140703517</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>9.325115577889449</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>8.805442211055276</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>7.515241206030151</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.643633165829145</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.282859296482413</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.190904522613066</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0.2287738693467336</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0.004180904522613061</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,49 +33408,49 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0279622641509434</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.270056603773585</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9627358490566039</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>2.641820754716981</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>4.515292452830189</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>6.071367924528302</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>7.084999999999999</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>7.272518867924529</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>6.652933962264151</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>5.33956603773585</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.569358490566038</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.736113207547171</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.5193867924528298</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1127075471698113</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0.001839622641509435</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.02344262295081967</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2084262295081968</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7049836065573772</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1.657393442622951</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>2.723606557377048</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>3.48527868852459</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.674737704918032</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.587360655737707</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.313508196721312</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.835278688524589</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.963</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.054065573770491</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.4085409836065572</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0.1001639344262295</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>0.001278688524590165</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.05226130653266328</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5352211055276379</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2.014804020100503</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>4.435613065326634</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>6.647834170854272</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>8.247226130653267</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>9.176628140703517</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>9.325115577889449</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>8.805442211055276</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>7.515241206030151</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.643633165829145</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.282859296482413</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.190904522613066</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0.2287738693467336</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0.004180904522613061</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,49 +33645,49 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0279622641509434</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.270056603773585</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9627358490566039</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>2.641820754716981</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>4.515292452830189</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>6.071367924528302</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>7.084999999999999</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>7.272518867924529</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>6.652933962264151</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>5.33956603773585</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.569358490566038</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.736113207547171</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.5193867924528298</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0.1127075471698113</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0.001839622641509435</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.02344262295081967</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2084262295081968</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7049836065573772</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1.657393442622951</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>2.723606557377048</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>3.48527868852459</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.674737704918032</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.587360655737707</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.313508196721312</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.835278688524589</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.963</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.054065573770491</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.4085409836065572</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0.1001639344262295</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0.001278688524590165</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.05226130653266328</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5352211055276379</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2.014804020100503</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>4.435613065326634</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>6.647834170854272</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>8.247226130653267</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>9.176628140703517</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>9.325115577889449</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>8.805442211055276</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>7.515241206030151</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.643633165829145</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.282859296482413</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.190904522613066</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0.2287738693467336</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0.004180904522613061</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,49 +33882,49 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0279622641509434</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.270056603773585</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9627358490566039</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>2.641820754716981</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>4.515292452830189</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>6.071367924528302</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>7.084999999999999</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>7.272518867924529</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>6.652933962264151</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>5.33956603773585</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.569358490566038</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.736113207547171</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.5193867924528298</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0.1127075471698113</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0.001839622641509435</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.02344262295081967</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2084262295081968</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7049836065573772</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1.657393442622951</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>2.723606557377048</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>3.48527868852459</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.674737704918032</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.587360655737707</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.313508196721312</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.835278688524589</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.963</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.054065573770491</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.4085409836065572</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0.1001639344262295</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0.001278688524590165</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.05226130653266328</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5352211055276379</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>2.014804020100503</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>4.435613065326634</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>6.647834170854272</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>8.247226130653267</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>9.176628140703517</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>9.325115577889449</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>8.805442211055276</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>7.515241206030151</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.643633165829145</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>3.282859296482413</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1.190904522613066</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0.2287738693467336</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0.004180904522613061</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,49 +34119,49 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0279622641509434</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.270056603773585</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9627358490566039</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>2.641820754716981</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>4.515292452830189</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>6.071367924528302</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>7.084999999999999</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>7.272518867924529</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>6.652933962264151</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>5.33956603773585</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.569358490566038</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.736113207547171</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.5193867924528298</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0.1127075471698113</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0.001839622641509435</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.02344262295081967</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2084262295081968</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7049836065573772</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1.657393442622951</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>2.723606557377048</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>3.48527868852459</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.674737704918032</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.587360655737707</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.313508196721312</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.835278688524589</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.963</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.054065573770491</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.4085409836065572</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0.1001639344262295</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0.001278688524590165</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.05226130653266328</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5352211055276379</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>2.014804020100503</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>4.435613065326634</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>6.647834170854272</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>8.247226130653267</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>9.176628140703517</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>9.325115577889449</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>8.805442211055276</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>7.515241206030151</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.643633165829145</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.282859296482413</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.190904522613066</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0.2287738693467336</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0.004180904522613061</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,49 +34356,49 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0279622641509434</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.270056603773585</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9627358490566039</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>2.641820754716981</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>4.515292452830189</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>6.071367924528302</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>7.084999999999999</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>7.272518867924529</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>6.652933962264151</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>5.33956603773585</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.569358490566038</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.736113207547171</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.5193867924528298</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0.1127075471698113</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0.001839622641509435</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.02344262295081967</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2084262295081968</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7049836065573772</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1.657393442622951</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>2.723606557377048</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>3.48527868852459</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.674737704918032</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.587360655737707</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.313508196721312</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.835278688524589</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.963</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.054065573770491</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.4085409836065572</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0.1001639344262295</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0.001278688524590165</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
